--- a/ZONE LIST.xlsx
+++ b/ZONE LIST.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1662f3d0eea558d6/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bijop\Downloads\PENDING-main\PENDING-1\C&amp;B PENDING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8A9FEF8-6A10-43C1-B2BB-FF0AAA8BC9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571CCE55-1E54-45FE-8ABF-75249AF178DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ZONE 1" sheetId="1" r:id="rId1"/>
-    <sheet name="ZONE 2" sheetId="3" r:id="rId2"/>
+    <sheet name="ZONE 1" sheetId="3" r:id="rId1"/>
+    <sheet name=" ZONE 2" sheetId="1" r:id="rId2"/>
     <sheet name="ZONE 3" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -433,41 +433,6 @@
   <dxfs count="18">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -524,6 +489,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -531,15 +505,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -581,22 +546,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -638,6 +587,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -645,78 +603,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -757,6 +643,120 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -771,30 +771,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2ECD370D-A800-492D-AA20-AB3070039861}" name="Table1" displayName="Table1" ref="A1:B23" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9D39F79-EE37-40FF-8E86-3432CF7B7CD5}" name="Table2" displayName="Table2" ref="A1:B23" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5B284719-FB1B-4716-AD88-988BBCB7833C}" name="S/No" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{EC8C07C1-7E9A-47D2-9CDA-E39BC02B1714}" name="AREA" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{F7181E63-3478-4B93-9313-BC08C6AAFE66}" name="S/No" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{F896B01C-E5F6-4BDA-A01E-3DE3B312D5D1}" name="AREA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9D39F79-EE37-40FF-8E86-3432CF7B7CD5}" name="Table2" displayName="Table2" ref="A1:B23" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2ECD370D-A800-492D-AA20-AB3070039861}" name="Table1" displayName="Table1" ref="A1:B23" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F7181E63-3478-4B93-9313-BC08C6AAFE66}" name="S/No" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{F896B01C-E5F6-4BDA-A01E-3DE3B312D5D1}" name="AREA" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{5B284719-FB1B-4716-AD88-988BBCB7833C}" name="S/No" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{EC8C07C1-7E9A-47D2-9CDA-E39BC02B1714}" name="AREA" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C5046E69-7142-415A-B31D-BBA0F8560C09}" name="Table3" displayName="Table3" ref="A1:B30" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C5046E69-7142-415A-B31D-BBA0F8560C09}" name="Table3" displayName="Table3" ref="A1:B30" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5036C359-D9AF-441E-9022-4F5C71F9E5D4}" name="S/No" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{CFC17631-F801-4BFF-BFE8-C93298CFDDB2}" name="AREA" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{5036C359-D9AF-441E-9022-4F5C71F9E5D4}" name="S/No" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{CFC17631-F801-4BFF-BFE8-C93298CFDDB2}" name="AREA" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1062,6 +1062,207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE475DF-FB96-42FB-8267-97A9AB0EEF3D}">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1252,207 +1453,6 @@
       </c>
       <c r="B23" s="6" t="s">
         <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE475DF-FB96-42FB-8267-97A9AB0EEF3D}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
